--- a/su25Vgrow1.xlsx
+++ b/su25Vgrow1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Kjuka_MasterThesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2765163D-6E24-44A6-BD56-31CDB73BD426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F54D996C-9E4B-45A7-9A60-4AA18BC15466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{01347F94-638F-4F43-94C8-500060006776}"/>
   </bookViews>
@@ -47,57 +47,6 @@
     <t>Plant_ID</t>
   </si>
   <si>
-    <t>VE</t>
-  </si>
-  <si>
-    <t>VC</t>
-  </si>
-  <si>
-    <t>V1</t>
-  </si>
-  <si>
-    <t>V2</t>
-  </si>
-  <si>
-    <t>V3</t>
-  </si>
-  <si>
-    <t>V4</t>
-  </si>
-  <si>
-    <t>V5</t>
-  </si>
-  <si>
-    <t>V6</t>
-  </si>
-  <si>
-    <t>V7</t>
-  </si>
-  <si>
-    <t>V8</t>
-  </si>
-  <si>
-    <t>V9</t>
-  </si>
-  <si>
-    <t>V10</t>
-  </si>
-  <si>
-    <t>V11</t>
-  </si>
-  <si>
-    <t>V12</t>
-  </si>
-  <si>
-    <t>V13</t>
-  </si>
-  <si>
-    <t>V14</t>
-  </si>
-  <si>
-    <t>V15</t>
-  </si>
-  <si>
     <t>N</t>
   </si>
   <si>
@@ -285,6 +234,57 @@
   </si>
   <si>
     <t>MP-Ex-5</t>
+  </si>
+  <si>
+    <t>V_1</t>
+  </si>
+  <si>
+    <t>V_2</t>
+  </si>
+  <si>
+    <t>V_3</t>
+  </si>
+  <si>
+    <t>V_4</t>
+  </si>
+  <si>
+    <t>V_5</t>
+  </si>
+  <si>
+    <t>V_6</t>
+  </si>
+  <si>
+    <t>V_7</t>
+  </si>
+  <si>
+    <t>V_8</t>
+  </si>
+  <si>
+    <t>V_9</t>
+  </si>
+  <si>
+    <t>V_10</t>
+  </si>
+  <si>
+    <t>V_11</t>
+  </si>
+  <si>
+    <t>V_12</t>
+  </si>
+  <si>
+    <t>V_13</t>
+  </si>
+  <si>
+    <t>V_14</t>
+  </si>
+  <si>
+    <t>V_15</t>
+  </si>
+  <si>
+    <t>V_16</t>
+  </si>
+  <si>
+    <t>V_17</t>
   </si>
 </sst>
 </file>
@@ -684,66 +684,66 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="L1" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="M1" t="s">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="N1" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="O1" t="s">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="P1" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="Q1" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="R1" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="S1" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="T1" t="s">
-        <v>19</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -788,24 +788,24 @@
         <v>12</v>
       </c>
       <c r="R2" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="S2" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T2" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -861,13 +861,13 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -918,18 +918,18 @@
         <v>12</v>
       </c>
       <c r="T4" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -971,27 +971,27 @@
         <v>10.5</v>
       </c>
       <c r="Q5" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="R5" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="S5" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T5" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1039,21 +1039,21 @@
         <v>11</v>
       </c>
       <c r="S6" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T6" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1104,18 +1104,18 @@
         <v>14</v>
       </c>
       <c r="T7" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1166,18 +1166,18 @@
         <v>12</v>
       </c>
       <c r="T8" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1219,27 +1219,27 @@
         <v>16</v>
       </c>
       <c r="Q9" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="R9" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="S9" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T9" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1287,21 +1287,21 @@
         <v>11</v>
       </c>
       <c r="S10" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T10" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1352,18 +1352,18 @@
         <v>11</v>
       </c>
       <c r="T11" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1411,21 +1411,21 @@
         <v>11</v>
       </c>
       <c r="S12" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T12" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1476,18 +1476,18 @@
         <v>11</v>
       </c>
       <c r="T13" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1535,21 +1535,21 @@
         <v>11</v>
       </c>
       <c r="S14" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T14" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" t="s">
         <v>20</v>
-      </c>
-      <c r="B15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" t="s">
-        <v>37</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1600,18 +1600,18 @@
         <v>13</v>
       </c>
       <c r="T15" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" t="s">
         <v>21</v>
-      </c>
-      <c r="C16" t="s">
-        <v>38</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1662,18 +1662,18 @@
         <v>12</v>
       </c>
       <c r="T16" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1718,24 +1718,24 @@
         <v>11</v>
       </c>
       <c r="R17" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="S17" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T17" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1780,24 +1780,24 @@
         <v>14</v>
       </c>
       <c r="R18" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="S18" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T18" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -1845,21 +1845,21 @@
         <v>11</v>
       </c>
       <c r="S19" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T19" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1907,21 +1907,21 @@
         <v>11</v>
       </c>
       <c r="S20" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T20" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1972,18 +1972,18 @@
         <v>11</v>
       </c>
       <c r="T21" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -2039,13 +2039,13 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -2096,18 +2096,18 @@
         <v>11</v>
       </c>
       <c r="T23" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -2152,24 +2152,24 @@
         <v>10</v>
       </c>
       <c r="R24" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="S24" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T24" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -2225,13 +2225,13 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -2282,18 +2282,18 @@
         <v>12</v>
       </c>
       <c r="T26" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -2349,13 +2349,13 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C28" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -2406,18 +2406,18 @@
         <v>11</v>
       </c>
       <c r="T28" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C29" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -2468,18 +2468,18 @@
         <v>12</v>
       </c>
       <c r="T29" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B30" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -2527,21 +2527,21 @@
         <v>11</v>
       </c>
       <c r="S30" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T30" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C31" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -2589,21 +2589,21 @@
         <v>11</v>
       </c>
       <c r="S31" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T31" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -2654,18 +2654,18 @@
         <v>13</v>
       </c>
       <c r="T32" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C33" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -2716,18 +2716,18 @@
         <v>11</v>
       </c>
       <c r="T33" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C34" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -2772,24 +2772,24 @@
         <v>10</v>
       </c>
       <c r="R34" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="S34" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T34" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C35" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -2837,21 +2837,21 @@
         <v>11</v>
       </c>
       <c r="S35" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T35" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C36" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -2899,21 +2899,21 @@
         <v>11</v>
       </c>
       <c r="S36" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T36" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C37" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -2955,27 +2955,27 @@
         <v>10</v>
       </c>
       <c r="Q37" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="R37" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="S37" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T37" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -3023,21 +3023,21 @@
         <v>12</v>
       </c>
       <c r="S38" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T38" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C39" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -3082,24 +3082,24 @@
         <v>11</v>
       </c>
       <c r="R39" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="S39" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T39" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C40" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -3147,21 +3147,21 @@
         <v>11</v>
       </c>
       <c r="S40" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T40" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C41" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -3206,24 +3206,24 @@
         <v>12</v>
       </c>
       <c r="R41" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="S41" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T41" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C42" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -3268,24 +3268,24 @@
         <v>12</v>
       </c>
       <c r="R42" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="S42" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T42" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C43" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -3333,21 +3333,21 @@
         <v>12</v>
       </c>
       <c r="S43" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T43" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C44" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -3398,18 +3398,18 @@
         <v>12</v>
       </c>
       <c r="T44" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C45" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -3448,30 +3448,30 @@
         <v>12</v>
       </c>
       <c r="P45" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="Q45" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="R45" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="S45" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T45" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B46" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C46" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -3513,27 +3513,27 @@
         <v>11</v>
       </c>
       <c r="Q46" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="R46" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="S46" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T46" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B47" t="s">
+        <v>36</v>
+      </c>
+      <c r="C47" t="s">
         <v>53</v>
-      </c>
-      <c r="C47" t="s">
-        <v>70</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -3584,18 +3584,18 @@
         <v>12</v>
       </c>
       <c r="T47" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B48" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C48" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -3643,21 +3643,21 @@
         <v>11</v>
       </c>
       <c r="S48" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T48" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C49" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -3708,18 +3708,18 @@
         <v>12</v>
       </c>
       <c r="T49" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C50" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -3767,21 +3767,21 @@
         <v>11</v>
       </c>
       <c r="S50" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T50" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B51" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C51" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -3829,21 +3829,21 @@
         <v>12</v>
       </c>
       <c r="S51" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T51" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B52" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C52" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -3894,18 +3894,18 @@
         <v>12</v>
       </c>
       <c r="T52" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C53" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -3961,13 +3961,13 @@
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B54" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C54" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -4018,18 +4018,18 @@
         <v>12</v>
       </c>
       <c r="T54" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B55" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C55" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -4077,21 +4077,21 @@
         <v>13</v>
       </c>
       <c r="S55" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T55" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B56" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C56" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -4139,21 +4139,21 @@
         <v>12</v>
       </c>
       <c r="S56" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T56" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B57" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C57" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -4201,21 +4201,21 @@
         <v>11</v>
       </c>
       <c r="S57" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T57" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B58" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C58" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -4257,27 +4257,27 @@
         <v>11</v>
       </c>
       <c r="Q58" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="R58" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="S58" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T58" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B59" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C59" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -4322,13 +4322,13 @@
         <v>11</v>
       </c>
       <c r="R59" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="S59" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="T59" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4571,20 +4571,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="772c1424-85c2-441a-bfd7-8f15f1cf8684" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="772c1424-85c2-441a-bfd7-8f15f1cf8684" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4607,6 +4607,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77BFA70F-E018-4F8C-B64D-1F44B4FD68AA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{929146D0-3490-4B96-B559-35C97FEFF40A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -4616,14 +4624,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77BFA70F-E018-4F8C-B64D-1F44B4FD68AA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{a2761ec8-7198-4440-bea0-e9dd2af28b51}" enabled="1" method="Standard" siteId="{73e15cf5-5dbb-46af-a862-753916269d73}" contentBits="0" removed="0"/>

--- a/su25Vgrow1.xlsx
+++ b/su25Vgrow1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Kjuka_MasterThesis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oia08\Documents\GitHub\Kjuka_MasterThesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F54D996C-9E4B-45A7-9A60-4AA18BC15466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A3FE328-673D-4731-97A0-B12249B13DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{01347F94-638F-4F43-94C8-500060006776}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{01347F94-638F-4F43-94C8-500060006776}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="82">
   <si>
     <t>Beetle</t>
   </si>
@@ -47,12 +47,6 @@
     <t>Plant_ID</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
     <t>C-Sb-1</t>
   </si>
   <si>
@@ -83,9 +77,6 @@
     <t>C-MBB-1</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>C-MBB-2</t>
   </si>
   <si>
@@ -146,9 +137,6 @@
     <t>C-Ex-5</t>
   </si>
   <si>
-    <t>MP</t>
-  </si>
-  <si>
     <t>MP-Sb-1</t>
   </si>
   <si>
@@ -285,6 +273,15 @@
   </si>
   <si>
     <t>V_17</t>
+  </si>
+  <si>
+    <t>No beetle</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Microplastic</t>
   </si>
 </sst>
 </file>
@@ -671,9 +668,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44F0C4B6-04E4-4AE1-9952-23977F00C22D}">
   <dimension ref="A1:T59"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -684,66 +681,66 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" t="s">
         <v>66</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>67</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>68</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>69</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>70</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
         <v>71</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" t="s">
         <v>72</v>
       </c>
-      <c r="K1" t="s">
+      <c r="O1" t="s">
         <v>73</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" t="s">
         <v>74</v>
       </c>
-      <c r="M1" t="s">
+      <c r="Q1" t="s">
         <v>75</v>
       </c>
-      <c r="N1" t="s">
+      <c r="R1" t="s">
         <v>76</v>
       </c>
-      <c r="O1" t="s">
+      <c r="S1" t="s">
         <v>77</v>
       </c>
-      <c r="P1" t="s">
+      <c r="T1" t="s">
         <v>78</v>
       </c>
-      <c r="Q1" t="s">
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="R1" t="s">
+      <c r="B2" t="s">
         <v>80</v>
       </c>
-      <c r="S1" t="s">
-        <v>81</v>
-      </c>
-      <c r="T1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -788,24 +785,24 @@
         <v>12</v>
       </c>
       <c r="R2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -859,15 +856,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -918,18 +915,18 @@
         <v>12</v>
       </c>
       <c r="T4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -971,27 +968,27 @@
         <v>10.5</v>
       </c>
       <c r="Q5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1039,21 +1036,21 @@
         <v>11</v>
       </c>
       <c r="S6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1104,18 +1101,18 @@
         <v>14</v>
       </c>
       <c r="T7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1166,18 +1163,18 @@
         <v>12</v>
       </c>
       <c r="T8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1219,27 +1216,27 @@
         <v>16</v>
       </c>
       <c r="Q9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1287,21 +1284,21 @@
         <v>11</v>
       </c>
       <c r="S10" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1352,18 +1349,18 @@
         <v>11</v>
       </c>
       <c r="T11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1411,21 +1408,21 @@
         <v>11</v>
       </c>
       <c r="S12" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" t="s">
         <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" t="s">
-        <v>18</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1476,18 +1473,18 @@
         <v>11</v>
       </c>
       <c r="T13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1535,21 +1532,21 @@
         <v>11</v>
       </c>
       <c r="S14" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B15" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1600,18 +1597,18 @@
         <v>13</v>
       </c>
       <c r="T15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1662,18 +1659,18 @@
         <v>12</v>
       </c>
       <c r="T16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1718,24 +1715,24 @@
         <v>11</v>
       </c>
       <c r="R17" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S17" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T17" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B18" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1780,24 +1777,24 @@
         <v>14</v>
       </c>
       <c r="R18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T18" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B19" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -1845,21 +1842,21 @@
         <v>11</v>
       </c>
       <c r="S19" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T19" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B20" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1907,21 +1904,21 @@
         <v>11</v>
       </c>
       <c r="S20" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T20" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1972,18 +1969,18 @@
         <v>11</v>
       </c>
       <c r="T21" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B22" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -2037,15 +2034,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -2096,18 +2093,18 @@
         <v>11</v>
       </c>
       <c r="T23" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -2152,24 +2149,24 @@
         <v>10</v>
       </c>
       <c r="R24" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S24" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -2223,15 +2220,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B26" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C26" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -2282,18 +2279,18 @@
         <v>12</v>
       </c>
       <c r="T26" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B27" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C27" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -2347,15 +2344,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B28" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C28" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -2406,18 +2403,18 @@
         <v>11</v>
       </c>
       <c r="T28" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B29" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -2468,18 +2465,18 @@
         <v>12</v>
       </c>
       <c r="T29" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B30" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C30" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -2527,21 +2524,21 @@
         <v>11</v>
       </c>
       <c r="S30" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T30" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C31" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -2589,21 +2586,21 @@
         <v>11</v>
       </c>
       <c r="S31" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T31" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C32" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -2654,18 +2651,18 @@
         <v>13</v>
       </c>
       <c r="T32" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C33" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -2716,18 +2713,18 @@
         <v>11</v>
       </c>
       <c r="T33" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B34" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" t="s">
         <v>36</v>
-      </c>
-      <c r="C34" t="s">
-        <v>40</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -2772,24 +2769,24 @@
         <v>10</v>
       </c>
       <c r="R34" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S34" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T34" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C35" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -2837,21 +2834,21 @@
         <v>11</v>
       </c>
       <c r="S35" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T35" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C36" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -2899,21 +2896,21 @@
         <v>11</v>
       </c>
       <c r="S36" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T36" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C37" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -2955,27 +2952,27 @@
         <v>10</v>
       </c>
       <c r="Q37" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R37" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S37" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T37" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C38" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -3023,21 +3020,21 @@
         <v>12</v>
       </c>
       <c r="S38" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T38" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B39" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C39" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -3082,24 +3079,24 @@
         <v>11</v>
       </c>
       <c r="R39" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S39" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T39" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C40" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -3147,21 +3144,21 @@
         <v>11</v>
       </c>
       <c r="S40" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B41" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C41" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -3206,24 +3203,24 @@
         <v>12</v>
       </c>
       <c r="R41" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S41" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T41" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C42" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -3268,24 +3265,24 @@
         <v>12</v>
       </c>
       <c r="R42" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S42" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T42" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C43" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -3333,21 +3330,21 @@
         <v>12</v>
       </c>
       <c r="S43" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T43" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B44" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C44" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -3398,18 +3395,18 @@
         <v>12</v>
       </c>
       <c r="T44" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B45" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C45" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -3448,30 +3445,30 @@
         <v>12</v>
       </c>
       <c r="P45" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q45" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R45" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S45" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T45" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C46" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -3513,27 +3510,27 @@
         <v>11</v>
       </c>
       <c r="Q46" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R46" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S46" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T46" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C47" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -3584,18 +3581,18 @@
         <v>12</v>
       </c>
       <c r="T47" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B48" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C48" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -3643,21 +3640,21 @@
         <v>11</v>
       </c>
       <c r="S48" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T48" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B49" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C49" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -3708,18 +3705,18 @@
         <v>12</v>
       </c>
       <c r="T49" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B50" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C50" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -3767,21 +3764,21 @@
         <v>11</v>
       </c>
       <c r="S50" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T50" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C51" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -3829,21 +3826,21 @@
         <v>12</v>
       </c>
       <c r="S51" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T51" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C52" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -3894,18 +3891,18 @@
         <v>12</v>
       </c>
       <c r="T52" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B53" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C53" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -3959,15 +3956,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C54" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -4018,18 +4015,18 @@
         <v>12</v>
       </c>
       <c r="T54" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B55" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C55" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -4077,21 +4074,21 @@
         <v>13</v>
       </c>
       <c r="S55" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T55" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B56" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C56" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -4139,21 +4136,21 @@
         <v>12</v>
       </c>
       <c r="S56" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T56" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B57" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C57" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -4201,21 +4198,21 @@
         <v>11</v>
       </c>
       <c r="S57" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T57" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B58" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C58" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -4257,27 +4254,27 @@
         <v>11</v>
       </c>
       <c r="Q58" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R58" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S58" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T58" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B59" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C59" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -4322,13 +4319,13 @@
         <v>11</v>
       </c>
       <c r="R59" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S59" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T59" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -4571,20 +4568,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="772c1424-85c2-441a-bfd7-8f15f1cf8684" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="772c1424-85c2-441a-bfd7-8f15f1cf8684" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4607,14 +4604,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77BFA70F-E018-4F8C-B64D-1F44B4FD68AA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{929146D0-3490-4B96-B559-35C97FEFF40A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -4624,6 +4613,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77BFA70F-E018-4F8C-B64D-1F44B4FD68AA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{a2761ec8-7198-4440-bea0-e9dd2af28b51}" enabled="1" method="Standard" siteId="{73e15cf5-5dbb-46af-a862-753916269d73}" contentBits="0" removed="0"/>
